--- a/test/fixtures/files/upload_single_page/05_combo_update_assay_samples_with_registered_assets_spreadsheet.xlsx
+++ b/test/fixtures/files/upload_single_page/05_combo_update_assay_samples_with_registered_assets_spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin.depelseneer/dev/projects/seek/test/fixtures/files/upload_single_page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B038824-F9D3-E94C-BD87-A2D24CADE0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A420A0CD-C3FC-ED4F-A68D-FF6FF053B39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Type Metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t>Study:</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>[{"id":10053,"type":"Sample","title":"Daisy"},{"id":10055,"type":"Sample","title":"Daffy"}]</t>
+  </si>
+  <si>
+    <t>Bramley</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1127,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="11" t="s">
@@ -11197,7 +11200,7 @@
       <c r="H1000" s="3"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" errorTitle="Input Error!" error="Please select one of the available options" promptTitle="organism" prompt="Choose a valid option. This value is REQUIRED!" sqref="F7:F1000 F5" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$F$2:$F$1918</formula1>
       <formula2>0</formula2>
